--- a/output/(山本)理解容易性_非曖昧性（一意性）_再構成.xlsx
+++ b/output/(山本)理解容易性_非曖昧性（一意性）_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,13 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>接続助詞「～し」や「～して」等の、並列、追加、原因、帰結などの複数の意味を持つ表現を避け、前後関係を一意に特定できる記述を行っている。</t>
+          <t>処理の実行順序が順次か並行かを実装者が一意に判定できるよう、文中に「〜し」「〜して」などの曖昧な接続助詞を用いず、シーケンス図やフローチャートの定義に準拠して実行順序または論理関係を明示している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】データを保存し、メールを送信する。（「保存した後に送信」か「保存と並行して送信」かが不明）
-→【適合例】データを保存した後に、メールを送信する。</t>
+          <t>★新規追加
+【非適合例】APIからデータを取得し、DBを更新する。（「〜し」という中止法を用いており、順次実行か並行実行か、あるいは原因と結果の因果関係かが特定できない。）
+→【適合例】APIからデータを取得した後、そのデータをDBに反映する。</t>
         </is>
       </c>
     </row>
@@ -479,13 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>「全ての」「必ずしも」等の修飾語と否定形を組み合わせる際、対象の全範囲を否定するのか一部を否定するのかが、文理上客観的に判別できる表現を選択している。</t>
+          <t>条件分岐の判定において、全体否定と部分否定の違いによる実装時の条件漏れを防ぐため、真理値表などの条件定義に基づき、論理演算子（AND、OR）の適用範囲が一意に特定できる構文を用いて記述している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】[例文2]全ての処理が成功しない場合は手順Cに進む。（「一部が失敗したとき」か「全てが失敗したとき」かが不明）
-→【適合例】[例文2a]1つ以上の処理が失敗した場合は、手順Cに進む。</t>
+          <t>【非適合例】［例文2］全ての処理が成功しない場合は手順Cに進む。（「全て〜ない」という表現では、全体否定か部分否定かが判別できない。）
+→【適合例1】［例文2a］全ての処理が失敗した場合は手順Cに進む。
+→【適合例2】［例文2b］どれか1つの処理が失敗した場合は手順Cに進む。</t>
         </is>
       </c>
     </row>
@@ -497,13 +499,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>図表、フローチャート、構成図等への言及において、それが既にある事実の「提示」なのか、設計上の構造を「定義・決定」するのか、その意図が明確になる動詞を選択している。</t>
+          <t>記述内容が仕様の前提事実か、あるいは本ドキュメントでの決定事項かを明確にするため、既存仕様の参照箇所と新規定義箇所を構造的または表現上明確に区別して記述している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】[例文1]プログラムの構造を図1に示す。（図1が構造の解説図なのか、構造を決定する設計図なのかが曖昧）
-→【適合例】[例文1b]図1の構成により、プログラムの構造を定義する。</t>
+          <t>【非適合例】［例文1］プログラムの構造を図1に示す。（既存の構造を図1に引用しているのか、図1をもって新たな構造を定義しているのかが特定できない。）
+→【適合例1】［例文1a］既存のプログラム構造を図示すると図1となる。
+→【適合例2】［例文1b］本機能のプログラム構造を図1のように定義する。</t>
         </is>
       </c>
     </row>
@@ -515,14 +518,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>修飾語と被修飾語を可能な限り隣接させ、かつ長い修飾語を文頭側に配置することで、係り受けの関係が単一の意味にのみ解釈できる語順を採用している。</t>
+          <t>複数の修飾対象が存在する文において、誤った対象への修飾による仕様の誤解を防ぐため、構文解析の原則に基づき、修飾語と被修飾語の対応関係を読点の挿入や語順の変更により一意に特定できる構造として記述している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】迅速に設計した仕様書を確認する。（「迅速に」が「設計」にかかるのか「確認」にかかるのかが不明確）
-→【適合例】設計が完了した仕様書の内容を、迅速に確認する。</t>
+【非適合例】暗号化されたDBのパスワードとユーザーIDを取得する。（係り受けの関係において、暗号化されている対象がパスワードだけか、ユーザーIDも含むのかが判別できない。）
+→【適合例】ユーザーIDと、暗号化されたDBのパスワードを取得する。</t>
         </is>
       </c>
     </row>
@@ -534,14 +537,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>文の「主語と述語」を可能な限り近接させ、一文の中に介在する要素を最小化することで、動作の主体と内容が即座に理解できる構造を維持している。</t>
+          <t>複雑な文構造による可読性の低下や実装時の見落としを防ぐため、主語と述語を近接して配置し、従属節や挿入句を含む長い文は複数の単文に分割して記述している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】本機能は、前回のリリースで実装された共通モジュールを呼び出すことで、ユーザーから入力されたデータのバリデーションを行う。（主語と述語が離れすぎている）
-→【適合例】本機能は、ユーザーの入力データをバリデーションする。その際、前回実装された共通モジュールを呼び出す。</t>
+【非適合例】システムは、外部APIから最新のユーザー情報を取得し、取得データ内でバリデーションエラーが発生しなかった場合のみ、DBの該当レコードを更新する。（主語である「システムは」と述語の「更新する」の間に別の条件節が介在し、文構造が複雑になっている。）
+→【適合例】システムは、外部APIから最新のユーザー情報を取得する。取得データ内でバリデーションエラーが発生しなかった場合のみ、システムはDBの該当レコードを更新する。</t>
         </is>
       </c>
     </row>
@@ -553,13 +556,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>句点（。）で区切られた一文の中で、表現する要件、動作、または定義を1つに限定し、論理的な意味単位（一文一義）を遵守して記述している。</t>
+          <t>エラーハンドリングや正常系の処理手順の実装漏れを防ぐため、1つの文に複数の条件や動作を連結せず、1文1義の原則に基づき、単一の操作や状態遷移ごとに分割して記述している。</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】ユーザーIDを入力してログインボタンを押下すると、認証サーバーに問い合わせが行われ、結果が画面に表示される。（入力、処理、表示が1文に混在）
-→【適合例】ユーザーIDを入力してログインボタンを押下する。システムは認証サーバーにIDの有効性を問い合わせ、その結果を画面に表示する。</t>
+          <t>★新規追加
+【非適合例】ユーザーがログインボタンを押下した際、入力値の検証を行い、エラーがあれば画面にメッセージを表示して、正常であればダッシュボード画面に遷移し、最終ログイン日時を更新する。（1つの文の中に分岐条件と複数の処理結果が混在しており、実装漏れを誘発する構造になっている。）
+→【適合例】ユーザーがログインボタンを押下した際、システムは入力値の検証を行う。エラーがある場合は、システムは画面にメッセージを表示する。正常な場合は、システムはダッシュボード画面に遷移する。画面遷移後、システムは最終ログイン日時を更新する。</t>
         </is>
       </c>
     </row>
@@ -571,13 +575,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>文書全体または用語定義集等の外部仕様に基づき、同一の概念、データ項目、機能名に対して、唯一の名称を継続して使用している。</t>
+          <t>ドメインモデルと実装コード間の不一致を防ぐため、プロジェクトの用語定義集やデータディクショナリに従い、同一の概念、データ項目、および画面コンポーネントには文書全体で一貫して同一の名称を記述している。</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】同一の概念に対して異なる名称が混在している。（「顧客ID」と「ユーザーコード」が同じ対象を指している状態）
-→【適合例】同一の対象に対し、文書全体で「顧客ID」という用語を統一して使用している。</t>
+          <t>★新規追加
+【非適合例】顧客IDを入力欄に設定する。その後、ユーザーIDを利用して外部APIを呼び出す。（同一のデータ項目に対して「顧客ID」と「ユーザーID」という異なる名称が混在しており、データマッピングの誤りを誘発する。）
+→【適合例】顧客IDを入力欄に設定する。その後、顧客IDを利用して外部APIを呼び出す。</t>
         </is>
       </c>
     </row>
@@ -589,13 +594,13 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>「前述」「上記」「前回」などの相対的な位置や順序を示す表現を排除し、参照先の章番号、項目名、または具体的な処理IDを明記して対象を特定している。</t>
+          <t>処理の再利用や参照関係における特定漏れを防ぐため、「これ」「前回」などの文脈に依存する抽象的な指示語を排除し、トレーサビリティマトリクスや仕様書内の特定の機能名およびトリガー条件を明記している。</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】［例文1］前回の処理と同様とする。（どの工程やステップを指すかが一意に特定できない）
-→【適合例】[例文1a]承認ボタンが押下されたときと同一の処理を実行する。</t>
+          <t>【非適合例】［例文1］前回の処理と同様とする。（指示語「前回」が指す処理内容や実行タイミングが実行環境や文脈により変化するため、対象を一意に特定できない。）
+→【適合例】［例文1a］承認ボタンが押下されたときと同じ処理を実行する。</t>
         </is>
       </c>
     </row>
@@ -607,68 +612,51 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>「来月」「現在」等の記述時点を基準とした直示表現を用いず、西暦や具体的な日付などの絶対的な指標を用いて時間的対象を確定している。</t>
+          <t>ドキュメントの参照時期によって生じる解釈のズレを完全に排除するため、日付や期間を「昨年」「来月」などの閲覧日に依存する相対表現で記述せず、西暦を用いた絶対的な日付フォーマットで明記している。</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】[例文2]昨年12月のリリース記録を参照。（「昨年」が指す年が、文書の閲覧時期によって変化する）
-→【適合例】[例文2a]2023年12月のリリース記録を参照する。</t>
+          <t>【非適合例】［例文2］昨年12月のリリース記録を参照する。（「昨年」という相対表現を用いており、ドキュメントの閲覧年によって指し示す年が変動してしまう。）
+→【適合例】［例文2a］2023年12月のリリース記録を参照する。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>指し示すものが明確である</t>
+          <t>表に空欄を残さない</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>指示代名詞（これ、それ等）の使用を最小限に留め、使用する場合はその指示対象が直前のどの語句を指しているかが客観的に一意に特定できる構文を選択している。</t>
+          <t>設定値やパラメータの定義漏れによる実装の滞りを防ぐため、値が存在しないテーブルのセルには空白を残さず、コーディング規約やドキュメント記述ルールに基づき「N/A」やハイフンなどの明示的な値を記述している。</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】サーバーの負荷が増大し、レスポンスが低下した。これがシステムの問題である。（「これ」が負荷増大かレスポンス低下かが不明確）
-→【適合例】サーバーの負荷が増大し、レスポンスが低下した。このレスポンスの低下が、本システムにおける改善課題である。</t>
+【非適合例】データ定義書の「初期値」列が空白のままとなっている。（空白の理由が、該当なし、未定、あるいは記入忘れのいずれであるかが判定できない。）
+→【適合例】データ定義書の「初期値」列において、初期値を持たない場合は「N/A」を記入する。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>表に空欄を残さない</t>
+          <t>状態とイベント（事象）を区別している</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>表形式の記載において、値が存在しない、未定、または該当しないセルに対し、特定の記号（「-」「N/A」「なし」等）を記入し、意図的な無記入であることを明示している。</t>
+          <t>状態検知（レベルトリガー）と状態変化の検知（エッジトリガー）の混同によるシステムの誤動作を防ぐため、状態遷移図やイベント定義に従い、継続している「状態」と、瞬間的な「状態の遷移（イベント）」を厳密に区別する用語を用いて記述している。</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】表内の空欄が、該当なし、未定（TBD）、記入漏れのいずれを意味するかが判別できない。（情報の欠落と意図的な空欄が区別不能）
-→【適合例】設定値が存在しないセルには、一律で「-」を記載する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>状態とイベント（事象）を区別している</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>システムの継続的な「状態（State）」と、変化の契機となる「事象（Event）」を、助詞「～のとき」と「～したとき」や、文末の表現を使い分けて厳格に区別している。</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>【非適合例】[例文1]電源ONのときに、処理Aを実行する。（「ONの状態」か「ONに切り替わった瞬間」かが曖昧）
-→【適合例】［例文１a］電源の状態がOFFからONに変化したときに、処理Aを実行する。</t>
+          <t>【非適合例】［例文1］電源ONのときに、バッチ処理を実行する。（「ONのときに」という表現では、ONである状態が継続している間なのか、OFFからONに切り替わった瞬間なのかが特定できない。）
+→【適合例1】［例文1a］電源がOFFからONに変わったときに、バッチ処理を実行する。（状態の遷移というイベントを明示している。）
+→【適合例2】［例文1b］電源がONの状態である間、バッチ処理を定期実行する。（継続している状態を明示している。）</t>
         </is>
       </c>
     </row>
